--- a/project/excel/linkml_pokemon.xlsx
+++ b/project/excel/linkml_pokemon.xlsx
@@ -7,41 +7,44 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Ability" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="BattleItem" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Berry" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="EggGroup" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Colour" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Flavor" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Food" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Game" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Generation" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Gym" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="GymLeader" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="HM" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="Habitat" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="HoldItem" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="Item" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="Pokedex" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="Pokemon" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="PokedexEntry" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="Pokeball" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet name="Place" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet name="Shape" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet name="Region" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet name="Species" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet name="Move" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet name="MoveLearning" sheetId="25" state="visible" r:id="rId25"/>
-    <sheet name="LearningByLevelingUp" sheetId="26" state="visible" r:id="rId26"/>
-    <sheet name="LearningThroughBreeding" sheetId="27" state="visible" r:id="rId27"/>
-    <sheet name="Medicine" sheetId="28" state="visible" r:id="rId28"/>
-    <sheet name="SpecialMove" sheetId="29" state="visible" r:id="rId29"/>
-    <sheet name="PhysicalMove" sheetId="30" state="visible" r:id="rId30"/>
-    <sheet name="StatusMove" sheetId="31" state="visible" r:id="rId31"/>
-    <sheet name="TM" sheetId="32" state="visible" r:id="rId32"/>
-    <sheet name="Town" sheetId="33" state="visible" r:id="rId33"/>
-    <sheet name="Trainer" sheetId="34" state="visible" r:id="rId34"/>
-    <sheet name="Type" sheetId="35" state="visible" r:id="rId35"/>
+    <sheet name="Thing" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="NamedThing" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Entity" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Ability" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="BattleItem" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Berry" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="EggGroup" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Colour" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Flavor" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Food" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Game" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Generation" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Gym" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="GymLeader" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="HM" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="Habitat" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="HoldItem" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="Item" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="Pokedex" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="Pokemon" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="PokedexEntry" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="Pokeball" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="Place" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet name="Shape" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet name="Region" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet name="Species" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet name="Move" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet name="MoveLearning" sheetId="28" state="visible" r:id="rId28"/>
+    <sheet name="LearningByLevelingUp" sheetId="29" state="visible" r:id="rId29"/>
+    <sheet name="LearningThroughBreeding" sheetId="30" state="visible" r:id="rId30"/>
+    <sheet name="Medicine" sheetId="31" state="visible" r:id="rId31"/>
+    <sheet name="SpecialMove" sheetId="32" state="visible" r:id="rId32"/>
+    <sheet name="PhysicalMove" sheetId="33" state="visible" r:id="rId33"/>
+    <sheet name="StatusMove" sheetId="34" state="visible" r:id="rId34"/>
+    <sheet name="TM" sheetId="35" state="visible" r:id="rId35"/>
+    <sheet name="Town" sheetId="36" state="visible" r:id="rId36"/>
+    <sheet name="Trainer" sheetId="37" state="visible" r:id="rId37"/>
+    <sheet name="Type" sheetId="38" state="visible" r:id="rId38"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -449,7 +452,15 @@
   </sheetPr>
   <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -488,7 +499,15 @@
   </sheetPr>
   <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>featuresSpecies</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -590,9 +609,27 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <dimension ref="A1:C1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -694,9 +731,32 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <dimension ref="A1:D1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>effectDescription</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -733,9 +793,27 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <dimension ref="A1:C1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -772,9 +850,32 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <dimension ref="A1:D1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>effectDescription</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -785,9 +886,32 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <dimension ref="A1:D1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>effectDescription</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -798,9 +922,32 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <dimension ref="A1:D1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>effectDescription</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -818,15 +965,77 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <dimension ref="A1:D1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>effectDescription</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -852,7 +1061,15 @@
   </sheetPr>
   <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>hasSize</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/project/excel/linkml_pokemon.xlsx
+++ b/project/excel/linkml_pokemon.xlsx
@@ -718,39 +718,86 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D1"/>
+  <dimension ref="A1:P1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>effectDescription</t>
+          <t>hasColour</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>mayHaveHiddenAbility</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>mayHaveAbility</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>isAbleToApply</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>hasHeight</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>hasWeight</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>depiction</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>inEggGroup</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>hasType</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>hasShape</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>hasGenus</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>hasCatchRate</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>foundIn</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
           <t>name</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
@@ -761,53 +808,37 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C1"/>
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>effectDescription</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>hasType</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
           <t>name</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
@@ -818,58 +849,53 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D1"/>
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>effectDescription</t>
+          <t>name</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>description</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
@@ -880,13 +906,39 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D1"/>
+<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -897,15 +949,20 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>hasType</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
           <t>name</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
@@ -916,13 +973,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D1"/>
+<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -933,15 +990,20 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>hasType</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
           <t>name</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
@@ -952,65 +1014,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D1"/>
+<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1021,15 +1031,20 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>hasType</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
           <t>name</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
@@ -1040,32 +1055,86 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A1"/>
+<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>hasSize</t>
+          <t>effectDescription</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>id</t>
         </is>
       </c>
     </row>
@@ -1074,6 +1143,40 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>hasSize</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/project/excel/linkml_pokemon.xlsx
+++ b/project/excel/linkml_pokemon.xlsx
@@ -7,44 +7,45 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Thing" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="NamedThing" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Entity" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Ability" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="BattleItem" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Berry" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="EggGroup" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Colour" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Flavor" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Food" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Game" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="Generation" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="Gym" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="GymLeader" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="HM" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="Habitat" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="HoldItem" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="Item" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="Pokedex" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet name="Pokemon" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet name="PokedexEntry" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet name="Pokeball" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet name="Place" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet name="Shape" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet name="Region" sheetId="25" state="visible" r:id="rId25"/>
-    <sheet name="Species" sheetId="26" state="visible" r:id="rId26"/>
-    <sheet name="Move" sheetId="27" state="visible" r:id="rId27"/>
-    <sheet name="MoveLearning" sheetId="28" state="visible" r:id="rId28"/>
-    <sheet name="LearningByLevelingUp" sheetId="29" state="visible" r:id="rId29"/>
-    <sheet name="LearningThroughBreeding" sheetId="30" state="visible" r:id="rId30"/>
-    <sheet name="Medicine" sheetId="31" state="visible" r:id="rId31"/>
-    <sheet name="SpecialMove" sheetId="32" state="visible" r:id="rId32"/>
-    <sheet name="PhysicalMove" sheetId="33" state="visible" r:id="rId33"/>
-    <sheet name="StatusMove" sheetId="34" state="visible" r:id="rId34"/>
-    <sheet name="TM" sheetId="35" state="visible" r:id="rId35"/>
-    <sheet name="Town" sheetId="36" state="visible" r:id="rId36"/>
-    <sheet name="Trainer" sheetId="37" state="visible" r:id="rId37"/>
-    <sheet name="Type" sheetId="38" state="visible" r:id="rId38"/>
+    <sheet name="Person" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Colour" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Thing" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="NamedThing" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Entity" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Ability" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="BattleItem" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Berry" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="EggGroup" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Flavor" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Food" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Game" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Generation" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="Gym" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="GymLeader" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="HM" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="Habitat" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="HoldItem" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="Item" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="Pokedex" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="Pokemon" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="PokedexEntry" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="Pokeball" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet name="Place" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet name="Shape" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet name="Region" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet name="Species" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet name="Move" sheetId="28" state="visible" r:id="rId28"/>
+    <sheet name="MoveLearning" sheetId="29" state="visible" r:id="rId29"/>
+    <sheet name="LearningByLevelingUp" sheetId="30" state="visible" r:id="rId30"/>
+    <sheet name="LearningThroughBreeding" sheetId="31" state="visible" r:id="rId31"/>
+    <sheet name="Medicine" sheetId="32" state="visible" r:id="rId32"/>
+    <sheet name="SpecialMove" sheetId="33" state="visible" r:id="rId33"/>
+    <sheet name="PhysicalMove" sheetId="34" state="visible" r:id="rId34"/>
+    <sheet name="StatusMove" sheetId="35" state="visible" r:id="rId35"/>
+    <sheet name="TM" sheetId="36" state="visible" r:id="rId36"/>
+    <sheet name="Town" sheetId="37" state="visible" r:id="rId37"/>
+    <sheet name="Trainer" sheetId="38" state="visible" r:id="rId38"/>
+    <sheet name="Type" sheetId="39" state="visible" r:id="rId39"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -452,15 +453,7 @@
   </sheetPr>
   <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -484,9 +477,27 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <dimension ref="A1:C1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -499,6 +510,19 @@
   </sheetPr>
   <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -512,19 +536,6 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -557,9 +568,27 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <dimension ref="A1:C1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -583,9 +612,27 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <dimension ref="A1:C1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -596,9 +643,27 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <dimension ref="A1:C1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -609,6 +674,58 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:C1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
@@ -634,58 +751,6 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -718,6 +783,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:P1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
@@ -808,7 +886,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -849,19 +927,6 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -881,6 +946,53 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:C1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
@@ -906,33 +1018,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -973,7 +1059,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1014,7 +1100,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1055,28 +1141,33 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <dimension ref="A1:C1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1107,12 +1198,87 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:C1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:D1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
@@ -1143,26 +1309,44 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A1"/>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1171,34 +1355,23 @@
           <t>hasSize</t>
         </is>
       </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/project/excel/linkml_pokemon.xlsx
+++ b/project/excel/linkml_pokemon.xlsx
@@ -9,39 +9,40 @@
   <sheets>
     <sheet name="Person" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Colour" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Ability" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="BattleItem" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Berry" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="EggGroup" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Flavor" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Food" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Game" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Generation" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Gym" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="GymLeader" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="HM" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="Habitat" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="HoldItem" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="Item" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="Pokedex" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="Pokemon" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="PokedexEntry" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet name="Pokeball" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet name="Shape" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet name="Region" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet name="Species" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet name="Move" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet name="MoveLearning" sheetId="25" state="visible" r:id="rId25"/>
-    <sheet name="LearningByLevelingUp" sheetId="26" state="visible" r:id="rId26"/>
-    <sheet name="LearningThroughBreeding" sheetId="27" state="visible" r:id="rId27"/>
-    <sheet name="Medicine" sheetId="28" state="visible" r:id="rId28"/>
-    <sheet name="SpecialMove" sheetId="29" state="visible" r:id="rId29"/>
-    <sheet name="PhysicalMove" sheetId="30" state="visible" r:id="rId30"/>
-    <sheet name="StatusMove" sheetId="31" state="visible" r:id="rId31"/>
-    <sheet name="TM" sheetId="32" state="visible" r:id="rId32"/>
-    <sheet name="Town" sheetId="33" state="visible" r:id="rId33"/>
-    <sheet name="Trainer" sheetId="34" state="visible" r:id="rId34"/>
-    <sheet name="Type" sheetId="35" state="visible" r:id="rId35"/>
+    <sheet name="Quantity" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Ability" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="BattleItem" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Berry" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="EggGroup" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Flavor" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Food" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Game" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Generation" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Gym" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="GymLeader" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="HM" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="Habitat" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="HoldItem" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="Item" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="Pokedex" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="Pokemon" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="PokedexEntry" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="Pokeball" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="Shape" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="Region" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet name="Species" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet name="Move" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet name="MoveLearning" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet name="LearningByLevelingUp" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet name="LearningThroughBreeding" sheetId="28" state="visible" r:id="rId28"/>
+    <sheet name="Medicine" sheetId="29" state="visible" r:id="rId29"/>
+    <sheet name="SpecialMove" sheetId="30" state="visible" r:id="rId30"/>
+    <sheet name="PhysicalMove" sheetId="31" state="visible" r:id="rId31"/>
+    <sheet name="StatusMove" sheetId="32" state="visible" r:id="rId32"/>
+    <sheet name="TM" sheetId="33" state="visible" r:id="rId33"/>
+    <sheet name="Town" sheetId="34" state="visible" r:id="rId34"/>
+    <sheet name="Trainer" sheetId="35" state="visible" r:id="rId35"/>
+    <sheet name="Type" sheetId="36" state="visible" r:id="rId36"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -483,6 +484,37 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:C1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:D1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
@@ -513,7 +545,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -544,7 +576,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -580,7 +612,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -611,7 +643,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -642,7 +674,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -673,7 +705,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -704,7 +736,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -735,7 +767,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -748,7 +780,93 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>black</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>cyanic</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>magenta</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>yellow</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>hue</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>saturation</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>wavelength</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -779,93 +897,276 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:N1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>black</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>cyanic</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>magenta</t>
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:P1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>hasColour</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>mayHaveHiddenAbility</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>mayHaveAbility</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>yellow</t>
+          <t>isAbleToApply</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>hue</t>
+          <t>hasHeight</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>saturation</t>
+          <t>hasWeight</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>value</t>
+          <t>depiction</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>red</t>
+          <t>inEggGroup</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>green</t>
+          <t>hasType</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>blue</t>
+          <t>hasShape</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>wavelength</t>
+          <t>hasGenus</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>hasCatchRate</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>foundIn</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>description</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>effectDescription</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>hasType</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -896,7 +1197,176 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>hasUnit</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>hasQuantityKind</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>hasValue</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>effectDescription</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>hasType</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>effectDescription</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>hasType</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>effectDescription</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>hasType</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -927,7 +1397,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -958,713 +1428,290 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:P1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>hasColour</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>mayHaveHiddenAbility</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>mayHaveAbility</t>
+<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>depiction</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>name</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>isAbleToApply</t>
+          <t>description</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>effectDescription</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>hasSize</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>hasFlavor</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>firmness</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>smoothness</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>hasHeight</t>
+          <t>id</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>hasWeight</t>
+          <t>name</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>depiction</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>inEggGroup</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>hasType</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>hasShape</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>hasGenus</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>hasCatchRate</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>foundIn</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>effectDescription</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>hasType</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>id</t>
+          <t>description</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>hasFlavor</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>firmness</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>smoothness</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>id</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>description</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>effectDescription</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>hasType</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>effectDescription</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>effectDescription</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>hasType</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>effectDescription</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>hasType</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>depiction</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:G1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>hasSize</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>hasFlavor</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>firmness</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>smoothness</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>id</t>
+          <t>name</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>hasFlavor</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>firmness</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>smoothness</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
           <t>description</t>
         </is>
       </c>
